--- a/artfynd/A 12375-2022 artfynd.xlsx
+++ b/artfynd/A 12375-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12375-2022 artfynd.xlsx
+++ b/artfynd/A 12375-2022 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112551582</v>
+        <v>112551562</v>
       </c>
       <c r="B2" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sydväst Tjärtjärnen, Vrm</t>
+          <t>Väst Tjärtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375323</v>
+        <v>375328</v>
       </c>
       <c r="R2" t="n">
-        <v>6699952</v>
+        <v>6700013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,16 +775,11 @@
         <v>112551566</v>
       </c>
       <c r="B3" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -882,16 +872,11 @@
         <v>112551572</v>
       </c>
       <c r="B4" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -981,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112551592</v>
+        <v>112551582</v>
       </c>
       <c r="B5" t="n">
-        <v>77772</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster Tjärtjärnen, Vrm</t>
+          <t>Sydväst Tjärtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375321</v>
+        <v>375322</v>
       </c>
       <c r="R5" t="n">
-        <v>6700054</v>
+        <v>6699951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112551562</v>
+        <v>112551586</v>
       </c>
       <c r="B6" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1119,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väst Tjärtjärnen, Vrm</t>
+          <t>Sydväst Tjärtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375328</v>
+        <v>375297</v>
       </c>
       <c r="R6" t="n">
-        <v>6700013</v>
+        <v>6699893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112551586</v>
+        <v>112551592</v>
       </c>
       <c r="B7" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst Tjärtjärnen, Vrm</t>
+          <t>Väster Tjärtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375297</v>
+        <v>375321</v>
       </c>
       <c r="R7" t="n">
-        <v>6699893</v>
+        <v>6700054</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 12375-2022 artfynd.xlsx
+++ b/artfynd/A 12375-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551566</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551572</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551582</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551586</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551592</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>